--- a/uploads/GB1001206_-_RATES.xlsx
+++ b/uploads/GB1001206_-_RATES.xlsx
@@ -1,23 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29212"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guruprasad_Mekala\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DFB587D-47E4-4A98-9B7D-578B22E2FCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{5DFB587D-47E4-4A98-9B7D-578B22E2FCC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8AD962-EEE2-4C24-BDA9-7B4B85B86A8F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ReportInfo" sheetId="1" r:id="rId1"/>
     <sheet name="PlanMaster View" sheetId="2" r:id="rId2"/>
     <sheet name="Product Definition-General View" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Product Definition-General View'!$A$1:$G$181</definedName>
+  </definedNames>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -250,7 +269,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-10409]m/d/yyyy"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -326,30 +345,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,7 +782,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
     <col min="2" max="2" width="0.5703125" customWidth="1"/>
@@ -775,43 +791,43 @@
     <col min="5" max="5" width="255" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8"/>
+    <row r="1" spans="1:3" ht="27.75" customHeight="1">
+      <c r="A1" s="7"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+    <row r="2" spans="1:3" ht="3" customHeight="1">
+      <c r="A2" s="7"/>
+    </row>
+    <row r="3" spans="1:3" ht="18" customHeight="1">
+      <c r="A3" s="7"/>
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-    </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
+    <row r="4" spans="1:3" ht="3" customHeight="1">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:3" ht="18" customHeight="1">
+      <c r="A5" s="7"/>
       <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
+    <row r="6" spans="1:3" ht="3" customHeight="1">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:3" ht="18" customHeight="1">
+      <c r="A7" s="7"/>
       <c r="C7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-    </row>
-    <row r="9" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" ht="33" customHeight="1">
+      <c r="A8" s="7"/>
+    </row>
+    <row r="9" spans="1:3" ht="25.5" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:A8"/>
@@ -826,7 +842,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AM11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="14" width="36.140625" customWidth="1"/>
@@ -834,8 +850,8 @@
     <col min="40" max="40" width="0.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="1:39" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" ht="6.6" customHeight="1"/>
+    <row r="2" spans="1:39" ht="38.25">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -954,7 +970,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39">
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
@@ -964,116 +980,116 @@
       <c r="C3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>80129399</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>19</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>87</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>6</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>1</v>
       </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6">
-        <v>0</v>
-      </c>
-      <c r="M3" s="6">
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
         <v>0</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="5">
         <v>0</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="5">
         <v>0</v>
       </c>
       <c r="R3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="6">
-        <v>0</v>
-      </c>
-      <c r="T3" s="6">
-        <v>0</v>
-      </c>
-      <c r="U3" s="6">
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
         <v>0</v>
       </c>
       <c r="V3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W3" s="6">
-        <v>0</v>
-      </c>
-      <c r="X3" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="6">
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="5">
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="6">
+      <c r="AA3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="5">
         <v>0</v>
       </c>
       <c r="AK3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL3" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39">
       <c r="A4" s="5" t="s">
         <v>43</v>
       </c>
@@ -1083,116 +1099,116 @@
       <c r="C4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>80129399</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>19</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>87</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>6</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>1</v>
       </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>0</v>
-      </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0</v>
-      </c>
-      <c r="M4" s="6">
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="5">
         <v>0</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="5">
         <v>0</v>
       </c>
       <c r="R4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6">
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
         <v>0</v>
       </c>
       <c r="V4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W4" s="6">
-        <v>0</v>
-      </c>
-      <c r="X4" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="6">
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5">
         <v>0</v>
       </c>
       <c r="Z4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="6">
+      <c r="AA4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="5">
         <v>0</v>
       </c>
       <c r="AK4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM4" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39">
       <c r="A5" s="5" t="s">
         <v>43</v>
       </c>
@@ -1202,116 +1218,116 @@
       <c r="C5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>80129399</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>19</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>87</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>6</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>1</v>
       </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
         <v>0</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="5">
         <v>1000</v>
       </c>
       <c r="P5" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="5">
         <v>25</v>
       </c>
       <c r="R5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="5">
         <v>1000</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="5">
         <v>25000</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="5">
         <v>0</v>
       </c>
       <c r="V5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W5" s="6">
-        <v>0</v>
-      </c>
-      <c r="X5" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="6">
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="5">
         <v>0</v>
       </c>
       <c r="Z5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AA5" s="5">
         <v>2</v>
       </c>
-      <c r="AB5" s="6">
+      <c r="AB5" s="5">
         <v>1</v>
       </c>
-      <c r="AC5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="6">
+      <c r="AC5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="5">
         <v>0</v>
       </c>
       <c r="AK5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL5" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39">
       <c r="A6" s="5" t="s">
         <v>43</v>
       </c>
@@ -1321,116 +1337,116 @@
       <c r="C6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>80129399</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>19</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>87</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>6</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>1</v>
       </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6">
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
         <v>0</v>
       </c>
       <c r="N6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="5">
         <v>1000</v>
       </c>
       <c r="P6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="5">
         <v>25</v>
       </c>
       <c r="R6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="5">
         <v>1000</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="5">
         <v>25000</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="5">
         <v>0</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W6" s="6">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6">
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5">
         <v>0</v>
       </c>
       <c r="Z6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AA6" s="5">
         <v>2</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="5">
         <v>7</v>
       </c>
-      <c r="AC6" s="6">
+      <c r="AC6" s="5">
         <v>1</v>
       </c>
-      <c r="AD6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="6">
+      <c r="AD6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="5">
         <v>0</v>
       </c>
       <c r="AK6" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM6" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39">
       <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
@@ -1440,116 +1456,116 @@
       <c r="C7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>80129399</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="5">
         <v>19</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>87</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>6</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>1</v>
       </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
         <v>0</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="5">
         <v>1000</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="5">
         <v>25</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S7" s="6">
+      <c r="S7" s="5">
         <v>1000</v>
       </c>
-      <c r="T7" s="6">
+      <c r="T7" s="5">
         <v>25000</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U7" s="5">
         <v>0</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W7" s="6">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6">
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5">
         <v>0</v>
       </c>
       <c r="Z7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AA7" s="5">
         <v>2</v>
       </c>
-      <c r="AB7" s="6">
+      <c r="AB7" s="5">
         <v>1</v>
       </c>
-      <c r="AC7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="6">
+      <c r="AC7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="5">
         <v>0</v>
       </c>
       <c r="AK7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL7" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -1559,116 +1575,116 @@
       <c r="C8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>80129399</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>19</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>87</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>6</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>1</v>
       </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
         <v>0</v>
       </c>
       <c r="N8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="O8" s="6">
+      <c r="O8" s="5">
         <v>0</v>
       </c>
       <c r="P8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="Q8" s="5">
         <v>0</v>
       </c>
       <c r="R8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
         <v>0</v>
       </c>
       <c r="V8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
         <v>0</v>
       </c>
       <c r="Z8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="6">
+      <c r="AA8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="5">
         <v>0</v>
       </c>
       <c r="AK8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39">
       <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
@@ -1678,116 +1694,116 @@
       <c r="C9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>80129399</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>19</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>87</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>6</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>1</v>
       </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
         <v>0</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="6">
+      <c r="O9" s="5">
         <v>0</v>
       </c>
       <c r="P9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="Q9" s="5">
         <v>0</v>
       </c>
       <c r="R9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S9" s="6">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6">
-        <v>0</v>
-      </c>
-      <c r="U9" s="6">
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
         <v>0</v>
       </c>
       <c r="V9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W9" s="6">
-        <v>0</v>
-      </c>
-      <c r="X9" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="6">
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
+      <c r="X9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="5">
         <v>0</v>
       </c>
       <c r="Z9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="6">
+      <c r="AA9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="5">
         <v>0</v>
       </c>
       <c r="AK9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL9" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39">
       <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
@@ -1797,116 +1813,116 @@
       <c r="C10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>80129399</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>19</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>87</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>6</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>1</v>
       </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>0</v>
-      </c>
-      <c r="M10" s="6">
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
         <v>0</v>
       </c>
       <c r="N10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="O10" s="6">
+      <c r="O10" s="5">
         <v>0</v>
       </c>
       <c r="P10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="Q10" s="5">
         <v>0</v>
       </c>
       <c r="R10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S10" s="6">
-        <v>0</v>
-      </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
         <v>0</v>
       </c>
       <c r="V10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W10" s="6">
-        <v>0</v>
-      </c>
-      <c r="X10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="6">
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
         <v>0</v>
       </c>
       <c r="Z10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="6">
+      <c r="AA10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="5">
         <v>0</v>
       </c>
       <c r="AK10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM10" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="AL10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39">
       <c r="A11" s="5" t="s">
         <v>43</v>
       </c>
@@ -1916,112 +1932,112 @@
       <c r="C11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>80129399</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>19</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>87</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>6</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>1</v>
       </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
         <v>0</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="O11" s="6">
+      <c r="O11" s="5">
         <v>0</v>
       </c>
       <c r="P11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="Q11" s="6">
+      <c r="Q11" s="5">
         <v>0</v>
       </c>
       <c r="R11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="S11" s="6">
-        <v>0</v>
-      </c>
-      <c r="T11" s="6">
-        <v>0</v>
-      </c>
-      <c r="U11" s="6">
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
         <v>0</v>
       </c>
       <c r="V11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="W11" s="6">
-        <v>0</v>
-      </c>
-      <c r="X11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="6">
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="5">
         <v>0</v>
       </c>
       <c r="Z11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AA11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="6">
+      <c r="AA11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="5">
         <v>0</v>
       </c>
       <c r="AK11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AL11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM11" s="6">
+      <c r="AL11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2034,14 +2050,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G183"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="13.7109375" customWidth="1"/>
     <col min="10" max="10" width="255" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="25.5">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -2064,7 +2081,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
         <v>43</v>
       </c>
@@ -2077,17 +2094,17 @@
       <c r="D2" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>38504</v>
       </c>
-      <c r="F2" s="6">
-        <v>65</v>
-      </c>
-      <c r="G2" s="6">
+      <c r="F2" s="5">
+        <v>65</v>
+      </c>
+      <c r="G2" s="5">
         <v>29.64</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
@@ -2100,17 +2117,17 @@
       <c r="D3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>38504</v>
       </c>
-      <c r="F3" s="6">
-        <v>65</v>
-      </c>
-      <c r="G3" s="6">
+      <c r="F3" s="5">
+        <v>65</v>
+      </c>
+      <c r="G3" s="5">
         <v>15.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
         <v>43</v>
       </c>
@@ -2123,17 +2140,17 @@
       <c r="D4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>38504</v>
       </c>
-      <c r="F4" s="6">
-        <v>65</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="F4" s="5">
+        <v>65</v>
+      </c>
+      <c r="G4" s="5">
         <v>40.56</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
         <v>43</v>
       </c>
@@ -2146,17 +2163,17 @@
       <c r="D5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>38504</v>
       </c>
-      <c r="F5" s="6">
-        <v>65</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" s="5">
+        <v>65</v>
+      </c>
+      <c r="G5" s="5">
         <v>29.64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
         <v>43</v>
       </c>
@@ -2169,17 +2186,17 @@
       <c r="D6" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>38504</v>
       </c>
-      <c r="F6" s="6">
-        <v>65</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="F6" s="5">
+        <v>65</v>
+      </c>
+      <c r="G6" s="5">
         <v>148.76</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
@@ -2192,17 +2209,17 @@
       <c r="D7" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>38504</v>
       </c>
-      <c r="F7" s="6">
-        <v>65</v>
-      </c>
-      <c r="G7" s="6">
+      <c r="F7" s="5">
+        <v>65</v>
+      </c>
+      <c r="G7" s="5">
         <v>78.3</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="5" t="s">
         <v>43</v>
       </c>
@@ -2215,17 +2232,17 @@
       <c r="D8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>38504</v>
       </c>
-      <c r="F8" s="6">
-        <v>65</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="F8" s="5">
+        <v>65</v>
+      </c>
+      <c r="G8" s="5">
         <v>203.56</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
@@ -2238,17 +2255,17 @@
       <c r="D9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>38504</v>
       </c>
-      <c r="F9" s="6">
-        <v>65</v>
-      </c>
-      <c r="G9" s="6">
+      <c r="F9" s="5">
+        <v>65</v>
+      </c>
+      <c r="G9" s="5">
         <v>148.76</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="5" t="s">
         <v>43</v>
       </c>
@@ -2261,17 +2278,17 @@
       <c r="D10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>38504</v>
       </c>
-      <c r="F10" s="6">
-        <v>65</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" s="5">
+        <v>65</v>
+      </c>
+      <c r="G10" s="5">
         <v>18.54</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="5" t="s">
         <v>43</v>
       </c>
@@ -2284,17 +2301,17 @@
       <c r="D11" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>38504</v>
       </c>
-      <c r="F11" s="6">
-        <v>65</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="F11" s="5">
+        <v>65</v>
+      </c>
+      <c r="G11" s="5">
         <v>9.76</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="5" t="s">
         <v>43</v>
       </c>
@@ -2307,17 +2324,17 @@
       <c r="D12" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>38504</v>
       </c>
-      <c r="F12" s="6">
-        <v>65</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12" s="5">
+        <v>65</v>
+      </c>
+      <c r="G12" s="5">
         <v>25.36</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
@@ -2330,17 +2347,17 @@
       <c r="D13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>38504</v>
       </c>
-      <c r="F13" s="6">
-        <v>65</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="F13" s="5">
+        <v>65</v>
+      </c>
+      <c r="G13" s="5">
         <v>18.54</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
@@ -2353,17 +2370,17 @@
       <c r="D14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>38504</v>
       </c>
-      <c r="F14" s="6">
-        <v>65</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="F14" s="5">
+        <v>65</v>
+      </c>
+      <c r="G14" s="5">
         <v>0.08</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
@@ -2376,17 +2393,17 @@
       <c r="D15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>38504</v>
       </c>
-      <c r="F15" s="6">
-        <v>65</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="F15" s="5">
+        <v>65</v>
+      </c>
+      <c r="G15" s="5">
         <v>0.44</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="A16" s="5" t="s">
         <v>43</v>
       </c>
@@ -2399,17 +2416,17 @@
       <c r="D16" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>38869</v>
       </c>
-      <c r="F16" s="6">
-        <v>65</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="F16" s="5">
+        <v>65</v>
+      </c>
+      <c r="G16" s="5">
         <v>36.74</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" s="5" t="s">
         <v>43</v>
       </c>
@@ -2422,17 +2439,17 @@
       <c r="D17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>38869</v>
       </c>
-      <c r="F17" s="6">
-        <v>65</v>
-      </c>
-      <c r="G17" s="6">
+      <c r="F17" s="5">
+        <v>65</v>
+      </c>
+      <c r="G17" s="5">
         <v>19.34</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
         <v>43</v>
       </c>
@@ -2445,17 +2462,17 @@
       <c r="D18" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>38869</v>
       </c>
-      <c r="F18" s="6">
-        <v>65</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18" s="5">
+        <v>65</v>
+      </c>
+      <c r="G18" s="5">
         <v>50.28</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
         <v>43</v>
       </c>
@@ -2468,17 +2485,17 @@
       <c r="D19" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>38869</v>
       </c>
-      <c r="F19" s="6">
-        <v>65</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="F19" s="5">
+        <v>65</v>
+      </c>
+      <c r="G19" s="5">
         <v>36.74</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
@@ -2491,17 +2508,17 @@
       <c r="D20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>39234</v>
       </c>
-      <c r="F20" s="6">
-        <v>65</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F20" s="5">
+        <v>65</v>
+      </c>
+      <c r="G20" s="5">
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" s="5" t="s">
         <v>43</v>
       </c>
@@ -2514,17 +2531,17 @@
       <c r="D21" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6">
         <v>39234</v>
       </c>
-      <c r="F21" s="6">
-        <v>65</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21" s="5">
+        <v>65</v>
+      </c>
+      <c r="G21" s="5">
         <v>12.1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
@@ -2537,17 +2554,17 @@
       <c r="D22" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="6">
         <v>39234</v>
       </c>
-      <c r="F22" s="6">
-        <v>65</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22" s="5">
+        <v>65</v>
+      </c>
+      <c r="G22" s="5">
         <v>31.48</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
         <v>43</v>
       </c>
@@ -2560,17 +2577,17 @@
       <c r="D23" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="6">
         <v>39234</v>
       </c>
-      <c r="F23" s="6">
-        <v>65</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="F23" s="5">
+        <v>65</v>
+      </c>
+      <c r="G23" s="5">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
@@ -2583,17 +2600,17 @@
       <c r="D24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>39234</v>
       </c>
-      <c r="F24" s="6">
-        <v>65</v>
-      </c>
-      <c r="G24" s="6">
+      <c r="F24" s="5">
+        <v>65</v>
+      </c>
+      <c r="G24" s="5">
         <v>184.47</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" s="5" t="s">
         <v>43</v>
       </c>
@@ -2606,17 +2623,17 @@
       <c r="D25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="6">
         <v>39234</v>
       </c>
-      <c r="F25" s="6">
-        <v>65</v>
-      </c>
-      <c r="G25" s="6">
+      <c r="F25" s="5">
+        <v>65</v>
+      </c>
+      <c r="G25" s="5">
         <v>97.1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="5" t="s">
         <v>43</v>
       </c>
@@ -2629,17 +2646,17 @@
       <c r="D26" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="6">
         <v>39234</v>
       </c>
-      <c r="F26" s="6">
-        <v>65</v>
-      </c>
-      <c r="G26" s="6">
+      <c r="F26" s="5">
+        <v>65</v>
+      </c>
+      <c r="G26" s="5">
         <v>252.48</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
@@ -2652,17 +2669,17 @@
       <c r="D27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="6">
         <v>39234</v>
       </c>
-      <c r="F27" s="6">
-        <v>65</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="F27" s="5">
+        <v>65</v>
+      </c>
+      <c r="G27" s="5">
         <v>184.47</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
@@ -2675,17 +2692,17 @@
       <c r="D28" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="6">
         <v>39234</v>
       </c>
-      <c r="F28" s="6">
-        <v>65</v>
-      </c>
-      <c r="G28" s="6">
+      <c r="F28" s="5">
+        <v>65</v>
+      </c>
+      <c r="G28" s="5">
         <v>36.74</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
@@ -2698,17 +2715,17 @@
       <c r="D29" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="6">
         <v>39234</v>
       </c>
-      <c r="F29" s="6">
-        <v>65</v>
-      </c>
-      <c r="G29" s="6">
+      <c r="F29" s="5">
+        <v>65</v>
+      </c>
+      <c r="G29" s="5">
         <v>19.34</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" s="5" t="s">
         <v>43</v>
       </c>
@@ -2721,17 +2738,17 @@
       <c r="D30" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="6">
         <v>39234</v>
       </c>
-      <c r="F30" s="6">
-        <v>65</v>
-      </c>
-      <c r="G30" s="6">
+      <c r="F30" s="5">
+        <v>65</v>
+      </c>
+      <c r="G30" s="5">
         <v>50.28</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="18">
       <c r="A31" s="5" t="s">
         <v>43</v>
       </c>
@@ -2744,17 +2761,17 @@
       <c r="D31" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="6">
         <v>39234</v>
       </c>
-      <c r="F31" s="6">
-        <v>65</v>
-      </c>
-      <c r="G31" s="6">
+      <c r="F31" s="5">
+        <v>65</v>
+      </c>
+      <c r="G31" s="5">
         <v>36.74</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="18">
       <c r="A32" s="5" t="s">
         <v>43</v>
       </c>
@@ -2767,17 +2784,17 @@
       <c r="D32" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="6">
         <v>40330</v>
       </c>
-      <c r="F32" s="6">
-        <v>65</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="F32" s="5">
+        <v>65</v>
+      </c>
+      <c r="G32" s="5">
         <v>40.409999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="18">
       <c r="A33" s="5" t="s">
         <v>43</v>
       </c>
@@ -2790,17 +2807,17 @@
       <c r="D33" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="7">
+      <c r="E33" s="6">
         <v>40330</v>
       </c>
-      <c r="F33" s="6">
-        <v>65</v>
-      </c>
-      <c r="G33" s="6">
+      <c r="F33" s="5">
+        <v>65</v>
+      </c>
+      <c r="G33" s="5">
         <v>21.27</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="18">
       <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
@@ -2813,17 +2830,17 @@
       <c r="D34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="7">
+      <c r="E34" s="6">
         <v>40330</v>
       </c>
-      <c r="F34" s="6">
-        <v>65</v>
-      </c>
-      <c r="G34" s="6">
+      <c r="F34" s="5">
+        <v>65</v>
+      </c>
+      <c r="G34" s="5">
         <v>55.31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="18">
       <c r="A35" s="5" t="s">
         <v>43</v>
       </c>
@@ -2836,17 +2853,17 @@
       <c r="D35" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="7">
+      <c r="E35" s="6">
         <v>40330</v>
       </c>
-      <c r="F35" s="6">
-        <v>65</v>
-      </c>
-      <c r="G35" s="6">
+      <c r="F35" s="5">
+        <v>65</v>
+      </c>
+      <c r="G35" s="5">
         <v>40.409999999999997</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="18">
       <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
@@ -2859,17 +2876,17 @@
       <c r="D36" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="7">
+      <c r="E36" s="6">
         <v>40330</v>
       </c>
-      <c r="F36" s="6">
-        <v>65</v>
-      </c>
-      <c r="G36" s="6">
+      <c r="F36" s="5">
+        <v>65</v>
+      </c>
+      <c r="G36" s="5">
         <v>202.92</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="18">
       <c r="A37" s="5" t="s">
         <v>43</v>
       </c>
@@ -2882,17 +2899,17 @@
       <c r="D37" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="6">
         <v>40330</v>
       </c>
-      <c r="F37" s="6">
-        <v>65</v>
-      </c>
-      <c r="G37" s="6">
+      <c r="F37" s="5">
+        <v>65</v>
+      </c>
+      <c r="G37" s="5">
         <v>106.81</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="18">
       <c r="A38" s="5" t="s">
         <v>43</v>
       </c>
@@ -2905,17 +2922,17 @@
       <c r="D38" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="7">
+      <c r="E38" s="6">
         <v>40330</v>
       </c>
-      <c r="F38" s="6">
-        <v>65</v>
-      </c>
-      <c r="G38" s="6">
+      <c r="F38" s="5">
+        <v>65</v>
+      </c>
+      <c r="G38" s="5">
         <v>277.73</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="18">
       <c r="A39" s="5" t="s">
         <v>43</v>
       </c>
@@ -2928,17 +2945,17 @@
       <c r="D39" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E39" s="7">
+      <c r="E39" s="6">
         <v>40330</v>
       </c>
-      <c r="F39" s="6">
-        <v>65</v>
-      </c>
-      <c r="G39" s="6">
+      <c r="F39" s="5">
+        <v>65</v>
+      </c>
+      <c r="G39" s="5">
         <v>202.92</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="18">
       <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
@@ -2951,17 +2968,17 @@
       <c r="D40" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="6">
         <v>40756</v>
       </c>
-      <c r="F40" s="6">
-        <v>65</v>
-      </c>
-      <c r="G40" s="6">
+      <c r="F40" s="5">
+        <v>65</v>
+      </c>
+      <c r="G40" s="5">
         <v>217.12</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="18">
       <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
@@ -2974,17 +2991,17 @@
       <c r="D41" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="6">
         <v>40756</v>
       </c>
-      <c r="F41" s="6">
-        <v>65</v>
-      </c>
-      <c r="G41" s="6">
+      <c r="F41" s="5">
+        <v>65</v>
+      </c>
+      <c r="G41" s="5">
         <v>114.29</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="18">
       <c r="A42" s="5" t="s">
         <v>43</v>
       </c>
@@ -2997,17 +3014,17 @@
       <c r="D42" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="6">
         <v>40756</v>
       </c>
-      <c r="F42" s="6">
-        <v>65</v>
-      </c>
-      <c r="G42" s="6">
+      <c r="F42" s="5">
+        <v>65</v>
+      </c>
+      <c r="G42" s="5">
         <v>24.61</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="18">
       <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
@@ -3020,17 +3037,17 @@
       <c r="D43" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="6">
         <v>40756</v>
       </c>
-      <c r="F43" s="6">
-        <v>65</v>
-      </c>
-      <c r="G43" s="6">
+      <c r="F43" s="5">
+        <v>65</v>
+      </c>
+      <c r="G43" s="5">
         <v>12.95</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="18">
       <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
@@ -3043,17 +3060,17 @@
       <c r="D44" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="6">
         <v>40756</v>
       </c>
-      <c r="F44" s="6">
-        <v>65</v>
-      </c>
-      <c r="G44" s="6">
+      <c r="F44" s="5">
+        <v>65</v>
+      </c>
+      <c r="G44" s="5">
         <v>33.68</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="18">
       <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
@@ -3066,17 +3083,17 @@
       <c r="D45" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="6">
         <v>40756</v>
       </c>
-      <c r="F45" s="6">
-        <v>65</v>
-      </c>
-      <c r="G45" s="6">
+      <c r="F45" s="5">
+        <v>65</v>
+      </c>
+      <c r="G45" s="5">
         <v>24.61</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="18">
       <c r="A46" s="5" t="s">
         <v>43</v>
       </c>
@@ -3089,17 +3106,17 @@
       <c r="D46" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="6">
         <v>40756</v>
       </c>
-      <c r="F46" s="6">
-        <v>65</v>
-      </c>
-      <c r="G46" s="6">
+      <c r="F46" s="5">
+        <v>65</v>
+      </c>
+      <c r="G46" s="5">
         <v>45.67</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="18">
       <c r="A47" s="5" t="s">
         <v>43</v>
       </c>
@@ -3112,17 +3129,17 @@
       <c r="D47" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="6">
         <v>40756</v>
       </c>
-      <c r="F47" s="6">
-        <v>65</v>
-      </c>
-      <c r="G47" s="6">
+      <c r="F47" s="5">
+        <v>65</v>
+      </c>
+      <c r="G47" s="5">
         <v>24.04</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="18">
       <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
@@ -3135,17 +3152,17 @@
       <c r="D48" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="6">
         <v>40756</v>
       </c>
-      <c r="F48" s="6">
-        <v>65</v>
-      </c>
-      <c r="G48" s="6">
+      <c r="F48" s="5">
+        <v>65</v>
+      </c>
+      <c r="G48" s="5">
         <v>62.5</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="18">
       <c r="A49" s="5" t="s">
         <v>43</v>
       </c>
@@ -3158,17 +3175,17 @@
       <c r="D49" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="6">
         <v>40756</v>
       </c>
-      <c r="F49" s="6">
-        <v>65</v>
-      </c>
-      <c r="G49" s="6">
+      <c r="F49" s="5">
+        <v>65</v>
+      </c>
+      <c r="G49" s="5">
         <v>45.67</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="18">
       <c r="A50" s="5" t="s">
         <v>43</v>
       </c>
@@ -3181,17 +3198,17 @@
       <c r="D50" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="6">
         <v>40756</v>
       </c>
-      <c r="F50" s="6">
-        <v>65</v>
-      </c>
-      <c r="G50" s="6">
+      <c r="F50" s="5">
+        <v>65</v>
+      </c>
+      <c r="G50" s="5">
         <v>297.17</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="18">
       <c r="A51" s="5" t="s">
         <v>43</v>
       </c>
@@ -3204,17 +3221,17 @@
       <c r="D51" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="6">
         <v>40756</v>
       </c>
-      <c r="F51" s="6">
-        <v>65</v>
-      </c>
-      <c r="G51" s="6">
+      <c r="F51" s="5">
+        <v>65</v>
+      </c>
+      <c r="G51" s="5">
         <v>217.12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="18">
       <c r="A52" s="5" t="s">
         <v>43</v>
       </c>
@@ -3227,17 +3244,17 @@
       <c r="D52" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="6">
         <v>41821</v>
       </c>
-      <c r="F52" s="6">
-        <v>65</v>
-      </c>
-      <c r="G52" s="6">
+      <c r="F52" s="5">
+        <v>65</v>
+      </c>
+      <c r="G52" s="5">
         <v>27.07</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="18">
       <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
@@ -3250,17 +3267,17 @@
       <c r="D53" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="6">
         <v>41821</v>
       </c>
-      <c r="F53" s="6">
-        <v>65</v>
-      </c>
-      <c r="G53" s="6">
+      <c r="F53" s="5">
+        <v>65</v>
+      </c>
+      <c r="G53" s="5">
         <v>14.25</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="18">
       <c r="A54" s="5" t="s">
         <v>43</v>
       </c>
@@ -3273,17 +3290,17 @@
       <c r="D54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="6">
         <v>41821</v>
       </c>
-      <c r="F54" s="6">
-        <v>65</v>
-      </c>
-      <c r="G54" s="6">
+      <c r="F54" s="5">
+        <v>65</v>
+      </c>
+      <c r="G54" s="5">
         <v>37.049999999999997</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="18">
       <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
@@ -3296,17 +3313,17 @@
       <c r="D55" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="6">
         <v>41821</v>
       </c>
-      <c r="F55" s="6">
-        <v>65</v>
-      </c>
-      <c r="G55" s="6">
+      <c r="F55" s="5">
+        <v>65</v>
+      </c>
+      <c r="G55" s="5">
         <v>27.07</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="18">
       <c r="A56" s="5" t="s">
         <v>43</v>
       </c>
@@ -3319,17 +3336,17 @@
       <c r="D56" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="6">
         <v>41821</v>
       </c>
-      <c r="F56" s="6">
-        <v>65</v>
-      </c>
-      <c r="G56" s="6">
+      <c r="F56" s="5">
+        <v>65</v>
+      </c>
+      <c r="G56" s="5">
         <v>238.83</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="18">
       <c r="A57" s="5" t="s">
         <v>43</v>
       </c>
@@ -3342,17 +3359,17 @@
       <c r="D57" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="6">
         <v>41821</v>
       </c>
-      <c r="F57" s="6">
-        <v>65</v>
-      </c>
-      <c r="G57" s="6">
+      <c r="F57" s="5">
+        <v>65</v>
+      </c>
+      <c r="G57" s="5">
         <v>326.89</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="18">
       <c r="A58" s="5" t="s">
         <v>43</v>
       </c>
@@ -3365,17 +3382,17 @@
       <c r="D58" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="6">
         <v>41821</v>
       </c>
-      <c r="F58" s="6">
-        <v>65</v>
-      </c>
-      <c r="G58" s="6">
+      <c r="F58" s="5">
+        <v>65</v>
+      </c>
+      <c r="G58" s="5">
         <v>125.72</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="18">
       <c r="A59" s="5" t="s">
         <v>43</v>
       </c>
@@ -3388,17 +3405,17 @@
       <c r="D59" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="6">
         <v>41821</v>
       </c>
-      <c r="F59" s="6">
-        <v>65</v>
-      </c>
-      <c r="G59" s="6">
+      <c r="F59" s="5">
+        <v>65</v>
+      </c>
+      <c r="G59" s="5">
         <v>238.83</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="18">
       <c r="A60" s="5" t="s">
         <v>43</v>
       </c>
@@ -3411,17 +3428,17 @@
       <c r="D60" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E60" s="7">
+      <c r="E60" s="6">
         <v>41821</v>
       </c>
-      <c r="F60" s="6">
-        <v>65</v>
-      </c>
-      <c r="G60" s="6">
+      <c r="F60" s="5">
+        <v>65</v>
+      </c>
+      <c r="G60" s="5">
         <v>50.24</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="18">
       <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
@@ -3434,17 +3451,17 @@
       <c r="D61" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E61" s="7">
+      <c r="E61" s="6">
         <v>41821</v>
       </c>
-      <c r="F61" s="6">
-        <v>65</v>
-      </c>
-      <c r="G61" s="6">
+      <c r="F61" s="5">
+        <v>65</v>
+      </c>
+      <c r="G61" s="5">
         <v>68.75</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="18">
       <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
@@ -3457,17 +3474,17 @@
       <c r="D62" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="6">
         <v>41821</v>
       </c>
-      <c r="F62" s="6">
-        <v>65</v>
-      </c>
-      <c r="G62" s="6">
+      <c r="F62" s="5">
+        <v>65</v>
+      </c>
+      <c r="G62" s="5">
         <v>26.44</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="18">
       <c r="A63" s="5" t="s">
         <v>43</v>
       </c>
@@ -3480,17 +3497,17 @@
       <c r="D63" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E63" s="7">
+      <c r="E63" s="6">
         <v>41821</v>
       </c>
-      <c r="F63" s="6">
-        <v>65</v>
-      </c>
-      <c r="G63" s="6">
+      <c r="F63" s="5">
+        <v>65</v>
+      </c>
+      <c r="G63" s="5">
         <v>50.24</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="18">
       <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
@@ -3503,17 +3520,17 @@
       <c r="D64" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="6">
         <v>42156</v>
       </c>
-      <c r="F64" s="6">
-        <v>65</v>
-      </c>
-      <c r="G64" s="6">
+      <c r="F64" s="5">
+        <v>65</v>
+      </c>
+      <c r="G64" s="5">
         <v>0.09</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="18">
       <c r="A65" s="5" t="s">
         <v>43</v>
       </c>
@@ -3526,17 +3543,17 @@
       <c r="D65" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E65" s="7">
+      <c r="E65" s="6">
         <v>42156</v>
       </c>
-      <c r="F65" s="6">
-        <v>65</v>
-      </c>
-      <c r="G65" s="6">
+      <c r="F65" s="5">
+        <v>65</v>
+      </c>
+      <c r="G65" s="5">
         <v>0.48</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="18">
       <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
@@ -3549,17 +3566,17 @@
       <c r="D66" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E66" s="7">
+      <c r="E66" s="6">
         <v>45809</v>
       </c>
-      <c r="F66" s="6">
-        <v>65</v>
-      </c>
-      <c r="G66" s="6">
+      <c r="F66" s="5">
+        <v>65</v>
+      </c>
+      <c r="G66" s="5">
         <v>80.150000000000006</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="18">
       <c r="A67" s="5" t="s">
         <v>43</v>
       </c>
@@ -3572,17 +3589,17 @@
       <c r="D67" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E67" s="7">
+      <c r="E67" s="6">
         <v>45809</v>
       </c>
-      <c r="F67" s="6">
-        <v>65</v>
-      </c>
-      <c r="G67" s="6">
+      <c r="F67" s="5">
+        <v>65</v>
+      </c>
+      <c r="G67" s="5">
         <v>109.69</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="18">
       <c r="A68" s="5" t="s">
         <v>43</v>
       </c>
@@ -3595,17 +3612,17 @@
       <c r="D68" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E68" s="7">
+      <c r="E68" s="6">
         <v>45809</v>
       </c>
-      <c r="F68" s="6">
-        <v>65</v>
-      </c>
-      <c r="G68" s="6">
+      <c r="F68" s="5">
+        <v>65</v>
+      </c>
+      <c r="G68" s="5">
         <v>80.150000000000006</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="18">
       <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
@@ -3618,17 +3635,17 @@
       <c r="D69" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E69" s="7">
+      <c r="E69" s="6">
         <v>45809</v>
       </c>
-      <c r="F69" s="6">
-        <v>65</v>
-      </c>
-      <c r="G69" s="6">
+      <c r="F69" s="5">
+        <v>65</v>
+      </c>
+      <c r="G69" s="5">
         <v>42.19</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="18">
       <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
@@ -3641,17 +3658,17 @@
       <c r="D70" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E70" s="7">
+      <c r="E70" s="6">
         <v>45809</v>
       </c>
-      <c r="F70" s="6">
-        <v>65</v>
-      </c>
-      <c r="G70" s="6">
+      <c r="F70" s="5">
+        <v>65</v>
+      </c>
+      <c r="G70" s="5">
         <v>381.05</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" ht="18">
       <c r="A71" s="5" t="s">
         <v>43</v>
       </c>
@@ -3664,17 +3681,17 @@
       <c r="D71" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E71" s="7">
+      <c r="E71" s="6">
         <v>45809</v>
       </c>
-      <c r="F71" s="6">
-        <v>65</v>
-      </c>
-      <c r="G71" s="6">
+      <c r="F71" s="5">
+        <v>65</v>
+      </c>
+      <c r="G71" s="5">
         <v>200.57</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" ht="18">
       <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
@@ -3687,17 +3704,17 @@
       <c r="D72" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E72" s="7">
+      <c r="E72" s="6">
         <v>45809</v>
       </c>
-      <c r="F72" s="6">
-        <v>65</v>
-      </c>
-      <c r="G72" s="6">
+      <c r="F72" s="5">
+        <v>65</v>
+      </c>
+      <c r="G72" s="5">
         <v>381.05</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" ht="18">
       <c r="A73" s="5" t="s">
         <v>43</v>
       </c>
@@ -3710,17 +3727,17 @@
       <c r="D73" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E73" s="7">
+      <c r="E73" s="6">
         <v>45809</v>
       </c>
-      <c r="F73" s="6">
-        <v>65</v>
-      </c>
-      <c r="G73" s="6">
+      <c r="F73" s="5">
+        <v>65</v>
+      </c>
+      <c r="G73" s="5">
         <v>521.53</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" ht="18">
       <c r="A74" s="5" t="s">
         <v>43</v>
       </c>
@@ -3733,17 +3750,17 @@
       <c r="D74" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E74" s="7">
+      <c r="E74" s="6">
         <v>45809</v>
       </c>
-      <c r="F74" s="6">
-        <v>65</v>
-      </c>
-      <c r="G74" s="6">
+      <c r="F74" s="5">
+        <v>65</v>
+      </c>
+      <c r="G74" s="5">
         <v>43.19</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="18">
       <c r="A75" s="5" t="s">
         <v>43</v>
       </c>
@@ -3756,17 +3773,17 @@
       <c r="D75" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E75" s="7">
+      <c r="E75" s="6">
         <v>45809</v>
       </c>
-      <c r="F75" s="6">
-        <v>65</v>
-      </c>
-      <c r="G75" s="6">
+      <c r="F75" s="5">
+        <v>65</v>
+      </c>
+      <c r="G75" s="5">
         <v>22.72</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" ht="18">
       <c r="A76" s="5" t="s">
         <v>43</v>
       </c>
@@ -3779,17 +3796,17 @@
       <c r="D76" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E76" s="7">
+      <c r="E76" s="6">
         <v>45809</v>
       </c>
-      <c r="F76" s="6">
-        <v>65</v>
-      </c>
-      <c r="G76" s="6">
+      <c r="F76" s="5">
+        <v>65</v>
+      </c>
+      <c r="G76" s="5">
         <v>59.12</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" ht="18">
       <c r="A77" s="5" t="s">
         <v>43</v>
       </c>
@@ -3802,17 +3819,17 @@
       <c r="D77" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E77" s="7">
+      <c r="E77" s="6">
         <v>45809</v>
       </c>
-      <c r="F77" s="6">
-        <v>65</v>
-      </c>
-      <c r="G77" s="6">
+      <c r="F77" s="5">
+        <v>65</v>
+      </c>
+      <c r="G77" s="5">
         <v>43.19</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" ht="18">
       <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
@@ -3825,17 +3842,17 @@
       <c r="D78" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E78" s="7">
+      <c r="E78" s="6">
         <v>42156</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="5">
         <v>66</v>
       </c>
-      <c r="G78" s="6">
+      <c r="G78" s="5">
         <v>0.48</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" ht="18">
       <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
@@ -3848,17 +3865,17 @@
       <c r="D79" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E79" s="7">
+      <c r="E79" s="6">
         <v>45809</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="5">
         <v>66</v>
       </c>
-      <c r="G79" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G79" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="18">
       <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
@@ -3871,17 +3888,17 @@
       <c r="D80" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E80" s="7">
+      <c r="E80" s="6">
         <v>45809</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80" s="5">
         <v>66</v>
       </c>
-      <c r="G80" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G80" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="18">
       <c r="A81" s="5" t="s">
         <v>43</v>
       </c>
@@ -3894,17 +3911,17 @@
       <c r="D81" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E81" s="7">
+      <c r="E81" s="6">
         <v>45809</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81" s="5">
         <v>66</v>
       </c>
-      <c r="G81" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G81" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="18">
       <c r="A82" s="5" t="s">
         <v>43</v>
       </c>
@@ -3917,17 +3934,17 @@
       <c r="D82" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E82" s="6">
         <v>45809</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82" s="5">
         <v>66</v>
       </c>
-      <c r="G82" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G82" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="18">
       <c r="A83" s="5" t="s">
         <v>43</v>
       </c>
@@ -3940,17 +3957,17 @@
       <c r="D83" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E83" s="7">
+      <c r="E83" s="6">
         <v>45809</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83" s="5">
         <v>66</v>
       </c>
-      <c r="G83" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G83" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="18">
       <c r="A84" s="5" t="s">
         <v>43</v>
       </c>
@@ -3963,17 +3980,17 @@
       <c r="D84" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E84" s="7">
+      <c r="E84" s="6">
         <v>45809</v>
       </c>
-      <c r="F84" s="6">
+      <c r="F84" s="5">
         <v>66</v>
       </c>
-      <c r="G84" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G84" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="18">
       <c r="A85" s="5" t="s">
         <v>43</v>
       </c>
@@ -3986,17 +4003,17 @@
       <c r="D85" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E85" s="7">
+      <c r="E85" s="6">
         <v>45809</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85" s="5">
         <v>66</v>
       </c>
-      <c r="G85" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G85" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="18">
       <c r="A86" s="5" t="s">
         <v>43</v>
       </c>
@@ -4009,17 +4026,17 @@
       <c r="D86" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E86" s="7">
+      <c r="E86" s="6">
         <v>45809</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86" s="5">
         <v>66</v>
       </c>
-      <c r="G86" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G86" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="18">
       <c r="A87" s="5" t="s">
         <v>43</v>
       </c>
@@ -4032,17 +4049,17 @@
       <c r="D87" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E87" s="7">
+      <c r="E87" s="6">
         <v>45809</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="5">
         <v>66</v>
       </c>
-      <c r="G87" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G87" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="18">
       <c r="A88" s="5" t="s">
         <v>43</v>
       </c>
@@ -4055,17 +4072,17 @@
       <c r="D88" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E88" s="7">
+      <c r="E88" s="6">
         <v>45809</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="5">
         <v>66</v>
       </c>
-      <c r="G88" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G88" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="18">
       <c r="A89" s="5" t="s">
         <v>43</v>
       </c>
@@ -4078,17 +4095,17 @@
       <c r="D89" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E89" s="7">
+      <c r="E89" s="6">
         <v>45809</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="5">
         <v>66</v>
       </c>
-      <c r="G89" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G89" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="18">
       <c r="A90" s="5" t="s">
         <v>43</v>
       </c>
@@ -4101,17 +4118,17 @@
       <c r="D90" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="6">
         <v>45809</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="5">
         <v>66</v>
       </c>
-      <c r="G90" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="G90" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="18">
       <c r="A91" s="5" t="s">
         <v>43</v>
       </c>
@@ -4124,17 +4141,17 @@
       <c r="D91" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E91" s="7">
+      <c r="E91" s="6">
         <v>42156</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="5">
         <v>69</v>
       </c>
-      <c r="G91" s="6">
+      <c r="G91" s="5">
         <v>0.48</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" ht="18">
       <c r="A92" s="5" t="s">
         <v>43</v>
       </c>
@@ -4147,17 +4164,17 @@
       <c r="D92" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E92" s="7">
+      <c r="E92" s="6">
         <v>45809</v>
       </c>
-      <c r="F92" s="6">
-        <v>99</v>
-      </c>
-      <c r="G92" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F92" s="5">
+        <v>99</v>
+      </c>
+      <c r="G92" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="18">
       <c r="A93" s="5" t="s">
         <v>43</v>
       </c>
@@ -4170,17 +4187,17 @@
       <c r="D93" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E93" s="7">
+      <c r="E93" s="6">
         <v>45809</v>
       </c>
-      <c r="F93" s="6">
-        <v>99</v>
-      </c>
-      <c r="G93" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F93" s="5">
+        <v>99</v>
+      </c>
+      <c r="G93" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="18">
       <c r="A94" s="5" t="s">
         <v>43</v>
       </c>
@@ -4193,17 +4210,17 @@
       <c r="D94" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E94" s="7">
+      <c r="E94" s="6">
         <v>45809</v>
       </c>
-      <c r="F94" s="6">
-        <v>99</v>
-      </c>
-      <c r="G94" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F94" s="5">
+        <v>99</v>
+      </c>
+      <c r="G94" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="18">
       <c r="A95" s="5" t="s">
         <v>43</v>
       </c>
@@ -4216,17 +4233,17 @@
       <c r="D95" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E95" s="7">
+      <c r="E95" s="6">
         <v>45809</v>
       </c>
-      <c r="F95" s="6">
-        <v>99</v>
-      </c>
-      <c r="G95" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F95" s="5">
+        <v>99</v>
+      </c>
+      <c r="G95" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="18">
       <c r="A96" s="5" t="s">
         <v>43</v>
       </c>
@@ -4239,17 +4256,17 @@
       <c r="D96" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E96" s="7">
+      <c r="E96" s="6">
         <v>45809</v>
       </c>
-      <c r="F96" s="6">
-        <v>99</v>
-      </c>
-      <c r="G96" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F96" s="5">
+        <v>99</v>
+      </c>
+      <c r="G96" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="18">
       <c r="A97" s="5" t="s">
         <v>43</v>
       </c>
@@ -4262,17 +4279,17 @@
       <c r="D97" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E97" s="7">
+      <c r="E97" s="6">
         <v>45809</v>
       </c>
-      <c r="F97" s="6">
-        <v>99</v>
-      </c>
-      <c r="G97" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F97" s="5">
+        <v>99</v>
+      </c>
+      <c r="G97" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="18">
       <c r="A98" s="5" t="s">
         <v>43</v>
       </c>
@@ -4285,17 +4302,17 @@
       <c r="D98" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E98" s="7">
+      <c r="E98" s="6">
         <v>45809</v>
       </c>
-      <c r="F98" s="6">
-        <v>99</v>
-      </c>
-      <c r="G98" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F98" s="5">
+        <v>99</v>
+      </c>
+      <c r="G98" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="18">
       <c r="A99" s="5" t="s">
         <v>43</v>
       </c>
@@ -4308,17 +4325,17 @@
       <c r="D99" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E99" s="7">
+      <c r="E99" s="6">
         <v>45809</v>
       </c>
-      <c r="F99" s="6">
-        <v>99</v>
-      </c>
-      <c r="G99" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F99" s="5">
+        <v>99</v>
+      </c>
+      <c r="G99" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="18">
       <c r="A100" s="5" t="s">
         <v>43</v>
       </c>
@@ -4331,17 +4348,17 @@
       <c r="D100" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E100" s="7">
+      <c r="E100" s="6">
         <v>45809</v>
       </c>
-      <c r="F100" s="6">
-        <v>99</v>
-      </c>
-      <c r="G100" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F100" s="5">
+        <v>99</v>
+      </c>
+      <c r="G100" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="18">
       <c r="A101" s="5" t="s">
         <v>43</v>
       </c>
@@ -4354,17 +4371,17 @@
       <c r="D101" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E101" s="7">
+      <c r="E101" s="6">
         <v>45809</v>
       </c>
-      <c r="F101" s="6">
-        <v>99</v>
-      </c>
-      <c r="G101" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F101" s="5">
+        <v>99</v>
+      </c>
+      <c r="G101" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="18">
       <c r="A102" s="5" t="s">
         <v>43</v>
       </c>
@@ -4377,17 +4394,17 @@
       <c r="D102" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E102" s="7">
+      <c r="E102" s="6">
         <v>45809</v>
       </c>
-      <c r="F102" s="6">
-        <v>99</v>
-      </c>
-      <c r="G102" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F102" s="5">
+        <v>99</v>
+      </c>
+      <c r="G102" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="18">
       <c r="A103" s="5" t="s">
         <v>43</v>
       </c>
@@ -4400,17 +4417,17 @@
       <c r="D103" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E103" s="7">
+      <c r="E103" s="6">
         <v>45809</v>
       </c>
-      <c r="F103" s="6">
-        <v>99</v>
-      </c>
-      <c r="G103" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+      <c r="F103" s="5">
+        <v>99</v>
+      </c>
+      <c r="G103" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="18" hidden="1">
       <c r="A104" s="5" t="s">
         <v>43</v>
       </c>
@@ -4423,17 +4440,17 @@
       <c r="D104" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E104" s="7">
+      <c r="E104" s="6">
         <v>42156</v>
       </c>
-      <c r="F104" s="6">
-        <v>65</v>
-      </c>
-      <c r="G104" s="6">
+      <c r="F104" s="5">
+        <v>65</v>
+      </c>
+      <c r="G104" s="5">
         <v>0.48</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="18" hidden="1">
       <c r="A105" s="5" t="s">
         <v>43</v>
       </c>
@@ -4446,17 +4463,17 @@
       <c r="D105" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E105" s="7">
+      <c r="E105" s="6">
         <v>38504</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="5">
         <v>69</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G105" s="5">
         <v>0.44</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" ht="18" hidden="1">
       <c r="A106" s="5" t="s">
         <v>43</v>
       </c>
@@ -4469,17 +4486,17 @@
       <c r="D106" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E106" s="7">
+      <c r="E106" s="6">
         <v>38504</v>
       </c>
-      <c r="F106" s="6">
-        <v>99</v>
-      </c>
-      <c r="G106" s="6">
+      <c r="F106" s="5">
+        <v>99</v>
+      </c>
+      <c r="G106" s="5">
         <v>29.66</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="18" hidden="1">
       <c r="A107" s="5" t="s">
         <v>43</v>
       </c>
@@ -4492,17 +4509,17 @@
       <c r="D107" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E107" s="7">
+      <c r="E107" s="6">
         <v>38504</v>
       </c>
-      <c r="F107" s="6">
-        <v>99</v>
-      </c>
-      <c r="G107" s="6">
+      <c r="F107" s="5">
+        <v>99</v>
+      </c>
+      <c r="G107" s="5">
         <v>15.62</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="18" hidden="1">
       <c r="A108" s="5" t="s">
         <v>43</v>
       </c>
@@ -4515,17 +4532,17 @@
       <c r="D108" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E108" s="7">
+      <c r="E108" s="6">
         <v>38504</v>
       </c>
-      <c r="F108" s="6">
-        <v>99</v>
-      </c>
-      <c r="G108" s="6">
+      <c r="F108" s="5">
+        <v>99</v>
+      </c>
+      <c r="G108" s="5">
         <v>40.56</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="18" hidden="1">
       <c r="A109" s="5" t="s">
         <v>43</v>
       </c>
@@ -4538,17 +4555,17 @@
       <c r="D109" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E109" s="7">
+      <c r="E109" s="6">
         <v>38504</v>
       </c>
-      <c r="F109" s="6">
-        <v>99</v>
-      </c>
-      <c r="G109" s="6">
+      <c r="F109" s="5">
+        <v>99</v>
+      </c>
+      <c r="G109" s="5">
         <v>29.66</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="18" hidden="1">
       <c r="A110" s="5" t="s">
         <v>43</v>
       </c>
@@ -4561,17 +4578,17 @@
       <c r="D110" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E110" s="7">
+      <c r="E110" s="6">
         <v>38504</v>
       </c>
-      <c r="F110" s="6">
-        <v>99</v>
-      </c>
-      <c r="G110" s="6">
+      <c r="F110" s="5">
+        <v>99</v>
+      </c>
+      <c r="G110" s="5">
         <v>47.42</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" ht="18" hidden="1">
       <c r="A111" s="5" t="s">
         <v>43</v>
       </c>
@@ -4584,17 +4601,17 @@
       <c r="D111" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E111" s="7">
+      <c r="E111" s="6">
         <v>38504</v>
       </c>
-      <c r="F111" s="6">
-        <v>99</v>
-      </c>
-      <c r="G111" s="6">
+      <c r="F111" s="5">
+        <v>99</v>
+      </c>
+      <c r="G111" s="5">
         <v>24.96</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" ht="18" hidden="1">
       <c r="A112" s="5" t="s">
         <v>43</v>
       </c>
@@ -4607,17 +4624,17 @@
       <c r="D112" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E112" s="7">
+      <c r="E112" s="6">
         <v>38504</v>
       </c>
-      <c r="F112" s="6">
-        <v>99</v>
-      </c>
-      <c r="G112" s="6">
+      <c r="F112" s="5">
+        <v>99</v>
+      </c>
+      <c r="G112" s="5">
         <v>64.900000000000006</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" ht="18" hidden="1">
       <c r="A113" s="5" t="s">
         <v>43</v>
       </c>
@@ -4630,17 +4647,17 @@
       <c r="D113" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E113" s="7">
+      <c r="E113" s="6">
         <v>38504</v>
       </c>
-      <c r="F113" s="6">
-        <v>99</v>
-      </c>
-      <c r="G113" s="6">
+      <c r="F113" s="5">
+        <v>99</v>
+      </c>
+      <c r="G113" s="5">
         <v>47.42</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="18" hidden="1">
       <c r="A114" s="5" t="s">
         <v>43</v>
       </c>
@@ -4653,17 +4670,17 @@
       <c r="D114" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E114" s="7">
+      <c r="E114" s="6">
         <v>38504</v>
       </c>
-      <c r="F114" s="6">
-        <v>99</v>
-      </c>
-      <c r="G114" s="6">
+      <c r="F114" s="5">
+        <v>99</v>
+      </c>
+      <c r="G114" s="5">
         <v>238</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="18" hidden="1">
       <c r="A115" s="5" t="s">
         <v>43</v>
       </c>
@@ -4676,17 +4693,17 @@
       <c r="D115" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E115" s="7">
+      <c r="E115" s="6">
         <v>38504</v>
       </c>
-      <c r="F115" s="6">
-        <v>99</v>
-      </c>
-      <c r="G115" s="6">
+      <c r="F115" s="5">
+        <v>99</v>
+      </c>
+      <c r="G115" s="5">
         <v>125.28</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" ht="18" hidden="1">
       <c r="A116" s="5" t="s">
         <v>43</v>
       </c>
@@ -4699,17 +4716,17 @@
       <c r="D116" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E116" s="7">
+      <c r="E116" s="6">
         <v>38504</v>
       </c>
-      <c r="F116" s="6">
-        <v>99</v>
-      </c>
-      <c r="G116" s="6">
+      <c r="F116" s="5">
+        <v>99</v>
+      </c>
+      <c r="G116" s="5">
         <v>325.7</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="18" hidden="1">
       <c r="A117" s="5" t="s">
         <v>43</v>
       </c>
@@ -4722,17 +4739,17 @@
       <c r="D117" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E117" s="7">
+      <c r="E117" s="6">
         <v>38504</v>
       </c>
-      <c r="F117" s="6">
-        <v>99</v>
-      </c>
-      <c r="G117" s="6">
+      <c r="F117" s="5">
+        <v>99</v>
+      </c>
+      <c r="G117" s="5">
         <v>238</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="18" hidden="1">
       <c r="A118" s="5" t="s">
         <v>43</v>
       </c>
@@ -4745,17 +4762,17 @@
       <c r="D118" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E118" s="7">
+      <c r="E118" s="6">
         <v>38869</v>
       </c>
-      <c r="F118" s="6">
-        <v>99</v>
-      </c>
-      <c r="G118" s="6">
+      <c r="F118" s="5">
+        <v>99</v>
+      </c>
+      <c r="G118" s="5">
         <v>58.82</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" ht="18" hidden="1">
       <c r="A119" s="5" t="s">
         <v>43</v>
       </c>
@@ -4768,17 +4785,17 @@
       <c r="D119" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E119" s="7">
+      <c r="E119" s="6">
         <v>38869</v>
       </c>
-      <c r="F119" s="6">
-        <v>99</v>
-      </c>
-      <c r="G119" s="6">
+      <c r="F119" s="5">
+        <v>99</v>
+      </c>
+      <c r="G119" s="5">
         <v>30.96</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="18" hidden="1">
       <c r="A120" s="5" t="s">
         <v>43</v>
       </c>
@@ -4791,17 +4808,17 @@
       <c r="D120" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E120" s="7">
+      <c r="E120" s="6">
         <v>38869</v>
       </c>
-      <c r="F120" s="6">
-        <v>99</v>
-      </c>
-      <c r="G120" s="6">
+      <c r="F120" s="5">
+        <v>99</v>
+      </c>
+      <c r="G120" s="5">
         <v>80.48</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="18" hidden="1">
       <c r="A121" s="5" t="s">
         <v>43</v>
       </c>
@@ -4814,17 +4831,17 @@
       <c r="D121" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E121" s="7">
+      <c r="E121" s="6">
         <v>38869</v>
       </c>
-      <c r="F121" s="6">
-        <v>99</v>
-      </c>
-      <c r="G121" s="6">
+      <c r="F121" s="5">
+        <v>99</v>
+      </c>
+      <c r="G121" s="5">
         <v>58.82</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="18" hidden="1">
       <c r="A122" s="5" t="s">
         <v>43</v>
       </c>
@@ -4837,17 +4854,17 @@
       <c r="D122" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E122" s="7">
+      <c r="E122" s="6">
         <v>39234</v>
       </c>
-      <c r="F122" s="6">
-        <v>99</v>
-      </c>
-      <c r="G122" s="6">
+      <c r="F122" s="5">
+        <v>99</v>
+      </c>
+      <c r="G122" s="5">
         <v>32.630000000000003</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" ht="18" hidden="1">
       <c r="A123" s="5" t="s">
         <v>43</v>
       </c>
@@ -4860,17 +4877,17 @@
       <c r="D123" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E123" s="7">
+      <c r="E123" s="6">
         <v>39234</v>
       </c>
-      <c r="F123" s="6">
-        <v>99</v>
-      </c>
-      <c r="G123" s="6">
+      <c r="F123" s="5">
+        <v>99</v>
+      </c>
+      <c r="G123" s="5">
         <v>17.18</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="18" hidden="1">
       <c r="A124" s="5" t="s">
         <v>43</v>
       </c>
@@ -4883,17 +4900,17 @@
       <c r="D124" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E124" s="7">
+      <c r="E124" s="6">
         <v>39234</v>
       </c>
-      <c r="F124" s="6">
-        <v>99</v>
-      </c>
-      <c r="G124" s="6">
+      <c r="F124" s="5">
+        <v>99</v>
+      </c>
+      <c r="G124" s="5">
         <v>44.62</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" ht="18" hidden="1">
       <c r="A125" s="5" t="s">
         <v>43</v>
       </c>
@@ -4906,17 +4923,17 @@
       <c r="D125" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E125" s="7">
+      <c r="E125" s="6">
         <v>39234</v>
       </c>
-      <c r="F125" s="6">
-        <v>99</v>
-      </c>
-      <c r="G125" s="6">
+      <c r="F125" s="5">
+        <v>99</v>
+      </c>
+      <c r="G125" s="5">
         <v>32.630000000000003</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" ht="18" hidden="1">
       <c r="A126" s="5" t="s">
         <v>43</v>
       </c>
@@ -4929,17 +4946,17 @@
       <c r="D126" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E126" s="7">
+      <c r="E126" s="6">
         <v>39234</v>
       </c>
-      <c r="F126" s="6">
-        <v>99</v>
-      </c>
-      <c r="G126" s="6">
+      <c r="F126" s="5">
+        <v>99</v>
+      </c>
+      <c r="G126" s="5">
         <v>34.06</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" ht="18" hidden="1">
       <c r="A127" s="5" t="s">
         <v>43</v>
       </c>
@@ -4952,17 +4969,17 @@
       <c r="D127" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E127" s="7">
+      <c r="E127" s="6">
         <v>39234</v>
       </c>
-      <c r="F127" s="6">
-        <v>99</v>
-      </c>
-      <c r="G127" s="6">
+      <c r="F127" s="5">
+        <v>99</v>
+      </c>
+      <c r="G127" s="5">
         <v>88.55</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="18" hidden="1">
       <c r="A128" s="5" t="s">
         <v>43</v>
       </c>
@@ -4975,17 +4992,17 @@
       <c r="D128" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E128" s="7">
+      <c r="E128" s="6">
         <v>39234</v>
       </c>
-      <c r="F128" s="6">
-        <v>99</v>
-      </c>
-      <c r="G128" s="6">
+      <c r="F128" s="5">
+        <v>99</v>
+      </c>
+      <c r="G128" s="5">
         <v>64.7</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="18" hidden="1">
       <c r="A129" s="5" t="s">
         <v>43</v>
       </c>
@@ -4998,17 +5015,17 @@
       <c r="D129" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E129" s="7">
+      <c r="E129" s="6">
         <v>39234</v>
       </c>
-      <c r="F129" s="6">
-        <v>99</v>
-      </c>
-      <c r="G129" s="6">
+      <c r="F129" s="5">
+        <v>99</v>
+      </c>
+      <c r="G129" s="5">
         <v>261.8</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="18" hidden="1">
       <c r="A130" s="5" t="s">
         <v>43</v>
       </c>
@@ -5021,17 +5038,17 @@
       <c r="D130" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E130" s="7">
+      <c r="E130" s="6">
         <v>39234</v>
       </c>
-      <c r="F130" s="6">
-        <v>99</v>
-      </c>
-      <c r="G130" s="6">
+      <c r="F130" s="5">
+        <v>99</v>
+      </c>
+      <c r="G130" s="5">
         <v>137.80000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="18" hidden="1">
       <c r="A131" s="5" t="s">
         <v>43</v>
       </c>
@@ -5044,17 +5061,17 @@
       <c r="D131" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E131" s="7">
+      <c r="E131" s="6">
         <v>39234</v>
       </c>
-      <c r="F131" s="6">
-        <v>99</v>
-      </c>
-      <c r="G131" s="6">
+      <c r="F131" s="5">
+        <v>99</v>
+      </c>
+      <c r="G131" s="5">
         <v>358.27</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="18" hidden="1">
       <c r="A132" s="5" t="s">
         <v>43</v>
       </c>
@@ -5067,17 +5084,17 @@
       <c r="D132" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E132" s="7">
+      <c r="E132" s="6">
         <v>39234</v>
       </c>
-      <c r="F132" s="6">
-        <v>99</v>
-      </c>
-      <c r="G132" s="6">
+      <c r="F132" s="5">
+        <v>99</v>
+      </c>
+      <c r="G132" s="5">
         <v>261.8</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="18" hidden="1">
       <c r="A133" s="5" t="s">
         <v>43</v>
       </c>
@@ -5090,17 +5107,17 @@
       <c r="D133" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E133" s="7">
+      <c r="E133" s="6">
         <v>39234</v>
       </c>
-      <c r="F133" s="6">
-        <v>99</v>
-      </c>
-      <c r="G133" s="6">
+      <c r="F133" s="5">
+        <v>99</v>
+      </c>
+      <c r="G133" s="5">
         <v>64.7</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="18" hidden="1">
       <c r="A134" s="5" t="s">
         <v>43</v>
       </c>
@@ -5113,17 +5130,17 @@
       <c r="D134" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E134" s="7">
+      <c r="E134" s="6">
         <v>40330</v>
       </c>
-      <c r="F134" s="6">
-        <v>99</v>
-      </c>
-      <c r="G134" s="6">
+      <c r="F134" s="5">
+        <v>99</v>
+      </c>
+      <c r="G134" s="5">
         <v>64.66</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="18" hidden="1">
       <c r="A135" s="5" t="s">
         <v>43</v>
       </c>
@@ -5136,17 +5153,17 @@
       <c r="D135" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E135" s="7">
+      <c r="E135" s="6">
         <v>40330</v>
       </c>
-      <c r="F135" s="6">
-        <v>99</v>
-      </c>
-      <c r="G135" s="6">
+      <c r="F135" s="5">
+        <v>99</v>
+      </c>
+      <c r="G135" s="5">
         <v>64.66</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="18" hidden="1">
       <c r="A136" s="5" t="s">
         <v>43</v>
       </c>
@@ -5159,17 +5176,17 @@
       <c r="D136" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E136" s="7">
+      <c r="E136" s="6">
         <v>40330</v>
       </c>
-      <c r="F136" s="6">
-        <v>99</v>
-      </c>
-      <c r="G136" s="6">
+      <c r="F136" s="5">
+        <v>99</v>
+      </c>
+      <c r="G136" s="5">
         <v>34.04</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="18" hidden="1">
       <c r="A137" s="5" t="s">
         <v>43</v>
       </c>
@@ -5182,17 +5199,17 @@
       <c r="D137" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E137" s="7">
+      <c r="E137" s="6">
         <v>40330</v>
       </c>
-      <c r="F137" s="6">
-        <v>99</v>
-      </c>
-      <c r="G137" s="6">
+      <c r="F137" s="5">
+        <v>99</v>
+      </c>
+      <c r="G137" s="5">
         <v>88.49</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="18" hidden="1">
       <c r="A138" s="5" t="s">
         <v>43</v>
       </c>
@@ -5205,17 +5222,17 @@
       <c r="D138" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E138" s="7">
+      <c r="E138" s="6">
         <v>40330</v>
       </c>
-      <c r="F138" s="6">
-        <v>99</v>
-      </c>
-      <c r="G138" s="6">
+      <c r="F138" s="5">
+        <v>99</v>
+      </c>
+      <c r="G138" s="5">
         <v>19.36</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="18" hidden="1">
       <c r="A139" s="5" t="s">
         <v>43</v>
       </c>
@@ -5228,17 +5245,17 @@
       <c r="D139" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E139" s="7">
+      <c r="E139" s="6">
         <v>40330</v>
       </c>
-      <c r="F139" s="6">
-        <v>99</v>
-      </c>
-      <c r="G139" s="6">
+      <c r="F139" s="5">
+        <v>99</v>
+      </c>
+      <c r="G139" s="5">
         <v>50.37</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="18" hidden="1">
       <c r="A140" s="5" t="s">
         <v>43</v>
       </c>
@@ -5251,17 +5268,17 @@
       <c r="D140" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E140" s="7">
+      <c r="E140" s="6">
         <v>40330</v>
       </c>
-      <c r="F140" s="6">
-        <v>99</v>
-      </c>
-      <c r="G140" s="6">
+      <c r="F140" s="5">
+        <v>99</v>
+      </c>
+      <c r="G140" s="5">
         <v>324.67</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="18" hidden="1">
       <c r="A141" s="5" t="s">
         <v>43</v>
       </c>
@@ -5274,17 +5291,17 @@
       <c r="D141" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E141" s="7">
+      <c r="E141" s="6">
         <v>40330</v>
       </c>
-      <c r="F141" s="6">
-        <v>99</v>
-      </c>
-      <c r="G141" s="6">
+      <c r="F141" s="5">
+        <v>99</v>
+      </c>
+      <c r="G141" s="5">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="18" hidden="1">
       <c r="A142" s="5" t="s">
         <v>43</v>
       </c>
@@ -5297,17 +5314,17 @@
       <c r="D142" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E142" s="7">
+      <c r="E142" s="6">
         <v>40330</v>
       </c>
-      <c r="F142" s="6">
-        <v>99</v>
-      </c>
-      <c r="G142" s="6">
+      <c r="F142" s="5">
+        <v>99</v>
+      </c>
+      <c r="G142" s="5">
         <v>324.67</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="18" hidden="1">
       <c r="A143" s="5" t="s">
         <v>43</v>
       </c>
@@ -5320,17 +5337,17 @@
       <c r="D143" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E143" s="7">
+      <c r="E143" s="6">
         <v>40330</v>
       </c>
-      <c r="F143" s="6">
-        <v>99</v>
-      </c>
-      <c r="G143" s="6">
+      <c r="F143" s="5">
+        <v>99</v>
+      </c>
+      <c r="G143" s="5">
         <v>170.9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" ht="18" hidden="1">
       <c r="A144" s="5" t="s">
         <v>43</v>
       </c>
@@ -5343,17 +5360,17 @@
       <c r="D144" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E144" s="7">
+      <c r="E144" s="6">
         <v>40330</v>
       </c>
-      <c r="F144" s="6">
-        <v>99</v>
-      </c>
-      <c r="G144" s="6">
+      <c r="F144" s="5">
+        <v>99</v>
+      </c>
+      <c r="G144" s="5">
         <v>444.36</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="18" hidden="1">
       <c r="A145" s="5" t="s">
         <v>43</v>
       </c>
@@ -5366,17 +5383,17 @@
       <c r="D145" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E145" s="7">
+      <c r="E145" s="6">
         <v>40330</v>
       </c>
-      <c r="F145" s="6">
-        <v>99</v>
-      </c>
-      <c r="G145" s="6">
+      <c r="F145" s="5">
+        <v>99</v>
+      </c>
+      <c r="G145" s="5">
         <v>36.799999999999997</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="18" hidden="1">
       <c r="A146" s="5" t="s">
         <v>43</v>
       </c>
@@ -5389,17 +5406,17 @@
       <c r="D146" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E146" s="7">
+      <c r="E146" s="6">
         <v>40756</v>
       </c>
-      <c r="F146" s="6">
-        <v>99</v>
-      </c>
-      <c r="G146" s="6">
+      <c r="F146" s="5">
+        <v>99</v>
+      </c>
+      <c r="G146" s="5">
         <v>379.96</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="18" hidden="1">
       <c r="A147" s="5" t="s">
         <v>43</v>
       </c>
@@ -5412,17 +5429,17 @@
       <c r="D147" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E147" s="7">
+      <c r="E147" s="6">
         <v>40756</v>
       </c>
-      <c r="F147" s="6">
-        <v>99</v>
-      </c>
-      <c r="G147" s="6">
+      <c r="F147" s="5">
+        <v>99</v>
+      </c>
+      <c r="G147" s="5">
         <v>200</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="18" hidden="1">
       <c r="A148" s="5" t="s">
         <v>43</v>
       </c>
@@ -5435,17 +5452,17 @@
       <c r="D148" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E148" s="7">
+      <c r="E148" s="6">
         <v>40756</v>
       </c>
-      <c r="F148" s="6">
-        <v>99</v>
-      </c>
-      <c r="G148" s="6">
+      <c r="F148" s="5">
+        <v>99</v>
+      </c>
+      <c r="G148" s="5">
         <v>520.04999999999995</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" ht="18" hidden="1">
       <c r="A149" s="5" t="s">
         <v>43</v>
       </c>
@@ -5458,17 +5475,17 @@
       <c r="D149" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E149" s="7">
+      <c r="E149" s="6">
         <v>40756</v>
       </c>
-      <c r="F149" s="6">
-        <v>99</v>
-      </c>
-      <c r="G149" s="6">
+      <c r="F149" s="5">
+        <v>99</v>
+      </c>
+      <c r="G149" s="5">
         <v>379.96</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="18" hidden="1">
       <c r="A150" s="5" t="s">
         <v>43</v>
       </c>
@@ -5481,17 +5498,17 @@
       <c r="D150" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E150" s="7">
+      <c r="E150" s="6">
         <v>40756</v>
       </c>
-      <c r="F150" s="6">
-        <v>99</v>
-      </c>
-      <c r="G150" s="6">
+      <c r="F150" s="5">
+        <v>99</v>
+      </c>
+      <c r="G150" s="5">
         <v>43.07</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="18" hidden="1">
       <c r="A151" s="5" t="s">
         <v>43</v>
       </c>
@@ -5504,17 +5521,17 @@
       <c r="D151" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E151" s="7">
+      <c r="E151" s="6">
         <v>40756</v>
       </c>
-      <c r="F151" s="6">
-        <v>99</v>
-      </c>
-      <c r="G151" s="6">
+      <c r="F151" s="5">
+        <v>99</v>
+      </c>
+      <c r="G151" s="5">
         <v>22.66</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="18" hidden="1">
       <c r="A152" s="5" t="s">
         <v>43</v>
       </c>
@@ -5527,17 +5544,17 @@
       <c r="D152" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E152" s="7">
+      <c r="E152" s="6">
         <v>40756</v>
       </c>
-      <c r="F152" s="6">
-        <v>99</v>
-      </c>
-      <c r="G152" s="6">
+      <c r="F152" s="5">
+        <v>99</v>
+      </c>
+      <c r="G152" s="5">
         <v>58.95</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="18" hidden="1">
       <c r="A153" s="5" t="s">
         <v>43</v>
       </c>
@@ -5550,17 +5567,17 @@
       <c r="D153" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E153" s="7">
+      <c r="E153" s="6">
         <v>40756</v>
       </c>
-      <c r="F153" s="6">
-        <v>99</v>
-      </c>
-      <c r="G153" s="6">
+      <c r="F153" s="5">
+        <v>99</v>
+      </c>
+      <c r="G153" s="5">
         <v>43.07</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="18" hidden="1">
       <c r="A154" s="5" t="s">
         <v>43</v>
       </c>
@@ -5573,17 +5590,17 @@
       <c r="D154" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E154" s="7">
+      <c r="E154" s="6">
         <v>40756</v>
       </c>
-      <c r="F154" s="6">
-        <v>99</v>
-      </c>
-      <c r="G154" s="6">
+      <c r="F154" s="5">
+        <v>99</v>
+      </c>
+      <c r="G154" s="5">
         <v>79.92</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="18" hidden="1">
       <c r="A155" s="5" t="s">
         <v>43</v>
       </c>
@@ -5596,17 +5613,17 @@
       <c r="D155" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E155" s="7">
+      <c r="E155" s="6">
         <v>40756</v>
       </c>
-      <c r="F155" s="6">
-        <v>99</v>
-      </c>
-      <c r="G155" s="6">
+      <c r="F155" s="5">
+        <v>99</v>
+      </c>
+      <c r="G155" s="5">
         <v>42.07</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" ht="18" hidden="1">
       <c r="A156" s="5" t="s">
         <v>43</v>
       </c>
@@ -5619,17 +5636,17 @@
       <c r="D156" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E156" s="7">
+      <c r="E156" s="6">
         <v>40756</v>
       </c>
-      <c r="F156" s="6">
-        <v>99</v>
-      </c>
-      <c r="G156" s="6">
+      <c r="F156" s="5">
+        <v>99</v>
+      </c>
+      <c r="G156" s="5">
         <v>109.37</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="18" hidden="1">
       <c r="A157" s="5" t="s">
         <v>43</v>
       </c>
@@ -5642,17 +5659,17 @@
       <c r="D157" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E157" s="7">
+      <c r="E157" s="6">
         <v>40756</v>
       </c>
-      <c r="F157" s="6">
-        <v>99</v>
-      </c>
-      <c r="G157" s="6">
+      <c r="F157" s="5">
+        <v>99</v>
+      </c>
+      <c r="G157" s="5">
         <v>79.92</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="18" hidden="1">
       <c r="A158" s="5" t="s">
         <v>43</v>
       </c>
@@ -5665,17 +5682,17 @@
       <c r="D158" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E158" s="7">
+      <c r="E158" s="6">
         <v>41821</v>
       </c>
-      <c r="F158" s="6">
-        <v>99</v>
-      </c>
-      <c r="G158" s="6">
+      <c r="F158" s="5">
+        <v>99</v>
+      </c>
+      <c r="G158" s="5">
         <v>417.96</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="18" hidden="1">
       <c r="A159" s="5" t="s">
         <v>43</v>
       </c>
@@ -5688,17 +5705,17 @@
       <c r="D159" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E159" s="7">
+      <c r="E159" s="6">
         <v>41821</v>
       </c>
-      <c r="F159" s="6">
-        <v>99</v>
-      </c>
-      <c r="G159" s="6">
+      <c r="F159" s="5">
+        <v>99</v>
+      </c>
+      <c r="G159" s="5">
         <v>47.38</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="18" hidden="1">
       <c r="A160" s="5" t="s">
         <v>43</v>
       </c>
@@ -5711,17 +5728,17 @@
       <c r="D160" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E160" s="7">
+      <c r="E160" s="6">
         <v>41821</v>
       </c>
-      <c r="F160" s="6">
-        <v>99</v>
-      </c>
-      <c r="G160" s="6">
+      <c r="F160" s="5">
+        <v>99</v>
+      </c>
+      <c r="G160" s="5">
         <v>64.849999999999994</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="18" hidden="1">
       <c r="A161" s="5" t="s">
         <v>43</v>
       </c>
@@ -5734,17 +5751,17 @@
       <c r="D161" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E161" s="7">
+      <c r="E161" s="6">
         <v>41821</v>
       </c>
-      <c r="F161" s="6">
-        <v>99</v>
-      </c>
-      <c r="G161" s="6">
+      <c r="F161" s="5">
+        <v>99</v>
+      </c>
+      <c r="G161" s="5">
         <v>417.96</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="18" hidden="1">
       <c r="A162" s="5" t="s">
         <v>43</v>
       </c>
@@ -5757,17 +5774,17 @@
       <c r="D162" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E162" s="7">
+      <c r="E162" s="6">
         <v>41821</v>
       </c>
-      <c r="F162" s="6">
-        <v>99</v>
-      </c>
-      <c r="G162" s="6">
+      <c r="F162" s="5">
+        <v>99</v>
+      </c>
+      <c r="G162" s="5">
         <v>572.05999999999995</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" ht="18" hidden="1">
       <c r="A163" s="5" t="s">
         <v>43</v>
       </c>
@@ -5780,17 +5797,17 @@
       <c r="D163" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E163" s="7">
+      <c r="E163" s="6">
         <v>41821</v>
       </c>
-      <c r="F163" s="6">
-        <v>99</v>
-      </c>
-      <c r="G163" s="6">
+      <c r="F163" s="5">
+        <v>99</v>
+      </c>
+      <c r="G163" s="5">
         <v>220</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="18" hidden="1">
       <c r="A164" s="5" t="s">
         <v>43</v>
       </c>
@@ -5803,17 +5820,17 @@
       <c r="D164" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E164" s="7">
+      <c r="E164" s="6">
         <v>41821</v>
       </c>
-      <c r="F164" s="6">
-        <v>99</v>
-      </c>
-      <c r="G164" s="6">
+      <c r="F164" s="5">
+        <v>99</v>
+      </c>
+      <c r="G164" s="5">
         <v>24.93</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="18" hidden="1">
       <c r="A165" s="5" t="s">
         <v>43</v>
       </c>
@@ -5826,17 +5843,17 @@
       <c r="D165" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E165" s="7">
+      <c r="E165" s="6">
         <v>41821</v>
       </c>
-      <c r="F165" s="6">
-        <v>99</v>
-      </c>
-      <c r="G165" s="6">
+      <c r="F165" s="5">
+        <v>99</v>
+      </c>
+      <c r="G165" s="5">
         <v>47.38</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="18" hidden="1">
       <c r="A166" s="5" t="s">
         <v>43</v>
       </c>
@@ -5849,17 +5866,17 @@
       <c r="D166" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E166" s="7">
+      <c r="E166" s="6">
         <v>41821</v>
       </c>
-      <c r="F166" s="6">
-        <v>99</v>
-      </c>
-      <c r="G166" s="6">
+      <c r="F166" s="5">
+        <v>99</v>
+      </c>
+      <c r="G166" s="5">
         <v>87.91</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="18" hidden="1">
       <c r="A167" s="5" t="s">
         <v>43</v>
       </c>
@@ -5872,17 +5889,17 @@
       <c r="D167" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E167" s="7">
+      <c r="E167" s="6">
         <v>41821</v>
       </c>
-      <c r="F167" s="6">
-        <v>99</v>
-      </c>
-      <c r="G167" s="6">
+      <c r="F167" s="5">
+        <v>99</v>
+      </c>
+      <c r="G167" s="5">
         <v>120.31</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="18" hidden="1">
       <c r="A168" s="5" t="s">
         <v>43</v>
       </c>
@@ -5895,17 +5912,17 @@
       <c r="D168" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E168" s="7">
+      <c r="E168" s="6">
         <v>41821</v>
       </c>
-      <c r="F168" s="6">
-        <v>99</v>
-      </c>
-      <c r="G168" s="6">
+      <c r="F168" s="5">
+        <v>99</v>
+      </c>
+      <c r="G168" s="5">
         <v>46.28</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="18" hidden="1">
       <c r="A169" s="5" t="s">
         <v>43</v>
       </c>
@@ -5918,17 +5935,17 @@
       <c r="D169" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E169" s="7">
+      <c r="E169" s="6">
         <v>41821</v>
       </c>
-      <c r="F169" s="6">
-        <v>99</v>
-      </c>
-      <c r="G169" s="6">
+      <c r="F169" s="5">
+        <v>99</v>
+      </c>
+      <c r="G169" s="5">
         <v>87.91</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" ht="18" hidden="1">
       <c r="A170" s="5" t="s">
         <v>43</v>
       </c>
@@ -5941,17 +5958,17 @@
       <c r="D170" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E170" s="7">
+      <c r="E170" s="6">
         <v>45809</v>
       </c>
-      <c r="F170" s="6">
-        <v>99</v>
-      </c>
-      <c r="G170" s="6">
+      <c r="F170" s="5">
+        <v>99</v>
+      </c>
+      <c r="G170" s="5">
         <v>140.25</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" ht="18" hidden="1">
       <c r="A171" s="5" t="s">
         <v>43</v>
       </c>
@@ -5964,17 +5981,17 @@
       <c r="D171" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E171" s="7">
+      <c r="E171" s="6">
         <v>45809</v>
       </c>
-      <c r="F171" s="6">
-        <v>99</v>
-      </c>
-      <c r="G171" s="6">
+      <c r="F171" s="5">
+        <v>99</v>
+      </c>
+      <c r="G171" s="5">
         <v>73.83</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="18" hidden="1">
       <c r="A172" s="5" t="s">
         <v>43</v>
       </c>
@@ -5987,17 +6004,17 @@
       <c r="D172" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E172" s="7">
+      <c r="E172" s="6">
         <v>45809</v>
       </c>
-      <c r="F172" s="6">
-        <v>99</v>
-      </c>
-      <c r="G172" s="6">
+      <c r="F172" s="5">
+        <v>99</v>
+      </c>
+      <c r="G172" s="5">
         <v>191.94</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="18" hidden="1">
       <c r="A173" s="5" t="s">
         <v>43</v>
       </c>
@@ -6010,17 +6027,17 @@
       <c r="D173" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E173" s="7">
+      <c r="E173" s="6">
         <v>45809</v>
       </c>
-      <c r="F173" s="6">
-        <v>99</v>
-      </c>
-      <c r="G173" s="6">
+      <c r="F173" s="5">
+        <v>99</v>
+      </c>
+      <c r="G173" s="5">
         <v>140.25</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="18" hidden="1">
       <c r="A174" s="5" t="s">
         <v>43</v>
       </c>
@@ -6033,17 +6050,17 @@
       <c r="D174" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E174" s="7">
+      <c r="E174" s="6">
         <v>45809</v>
       </c>
-      <c r="F174" s="6">
-        <v>99</v>
-      </c>
-      <c r="G174" s="6">
+      <c r="F174" s="5">
+        <v>99</v>
+      </c>
+      <c r="G174" s="5">
         <v>666.83</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="18" hidden="1">
       <c r="A175" s="5" t="s">
         <v>43</v>
       </c>
@@ -6056,17 +6073,17 @@
       <c r="D175" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E175" s="7">
+      <c r="E175" s="6">
         <v>45809</v>
       </c>
-      <c r="F175" s="6">
-        <v>99</v>
-      </c>
-      <c r="G175" s="6">
+      <c r="F175" s="5">
+        <v>99</v>
+      </c>
+      <c r="G175" s="5">
         <v>351</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="18" hidden="1">
       <c r="A176" s="5" t="s">
         <v>43</v>
       </c>
@@ -6079,17 +6096,17 @@
       <c r="D176" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E176" s="7">
+      <c r="E176" s="6">
         <v>45809</v>
       </c>
-      <c r="F176" s="6">
-        <v>99</v>
-      </c>
-      <c r="G176" s="6">
+      <c r="F176" s="5">
+        <v>99</v>
+      </c>
+      <c r="G176" s="5">
         <v>912.68</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="18" hidden="1">
       <c r="A177" s="5" t="s">
         <v>43</v>
       </c>
@@ -6102,17 +6119,17 @@
       <c r="D177" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E177" s="7">
+      <c r="E177" s="6">
         <v>45809</v>
       </c>
-      <c r="F177" s="6">
-        <v>99</v>
-      </c>
-      <c r="G177" s="6">
+      <c r="F177" s="5">
+        <v>99</v>
+      </c>
+      <c r="G177" s="5">
         <v>666.83</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="18" hidden="1">
       <c r="A178" s="5" t="s">
         <v>43</v>
       </c>
@@ -6125,17 +6142,17 @@
       <c r="D178" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E178" s="7">
+      <c r="E178" s="6">
         <v>45809</v>
       </c>
-      <c r="F178" s="6">
-        <v>99</v>
-      </c>
-      <c r="G178" s="6">
+      <c r="F178" s="5">
+        <v>99</v>
+      </c>
+      <c r="G178" s="5">
         <v>75.59</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="18" hidden="1">
       <c r="A179" s="5" t="s">
         <v>43</v>
       </c>
@@ -6148,17 +6165,17 @@
       <c r="D179" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E179" s="7">
+      <c r="E179" s="6">
         <v>45809</v>
       </c>
-      <c r="F179" s="6">
-        <v>99</v>
-      </c>
-      <c r="G179" s="6">
+      <c r="F179" s="5">
+        <v>99</v>
+      </c>
+      <c r="G179" s="5">
         <v>39.76</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="18" hidden="1">
       <c r="A180" s="5" t="s">
         <v>43</v>
       </c>
@@ -6171,17 +6188,17 @@
       <c r="D180" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E180" s="7">
+      <c r="E180" s="6">
         <v>45809</v>
       </c>
-      <c r="F180" s="6">
-        <v>99</v>
-      </c>
-      <c r="G180" s="6">
+      <c r="F180" s="5">
+        <v>99</v>
+      </c>
+      <c r="G180" s="5">
         <v>103.45</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" ht="18" hidden="1">
       <c r="A181" s="5" t="s">
         <v>43</v>
       </c>
@@ -6194,19 +6211,26 @@
       <c r="D181" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E181" s="7">
+      <c r="E181" s="6">
         <v>45809</v>
       </c>
-      <c r="F181" s="6">
-        <v>99</v>
-      </c>
-      <c r="G181" s="6">
+      <c r="F181" s="5">
+        <v>99</v>
+      </c>
+      <c r="G181" s="5">
         <v>75.59</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="183" spans="1:7" ht="11.85" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" spans="1:7" ht="0" hidden="1" customHeight="1"/>
+    <row r="183" spans="1:7" ht="11.85" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="A1:G181" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="0000001"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="1" right="1" top="1" bottom="1" header="1" footer="1"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
